--- a/agent_runs/manjidiwang/episodes/ep13/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep13/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>办公室茶具碎裂（，总时长：11秒，镜头数：4个）</t>
+          <t>办公室茶具碎裂</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>天香楼硬菜（，总时长：10秒，镜头数：4个）</t>
+          <t>天香楼硬菜</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>包厢屏蔽谈判（，总时长：10秒，镜头数：5个）</t>
+          <t>包厢屏蔽谈判</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>城南烂账交锋（，总时长：11秒，镜头数：5个）</t>
+          <t>城南烂账交锋</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>至亲亦可杀（，总时长：12秒，镜头数：6个）</t>
+          <t>至亲亦可杀</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>门口电话谈崩（，总时长：11秒，镜头数：5个）</t>
+          <t>门口电话谈崩</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>借债局收网（，总时长：10秒，镜头数：5个）</t>
+          <t>借债局收网</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
